--- a/testakten/kaufrecht-smartwatch-gesundheitsabo-update-hannover/xlsx/mangel_und_update_matrix.xlsx
+++ b/testakten/kaufrecht-smartwatch-gesundheitsabo-update-hannover/xlsx/mangel_und_update_matrix.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kosten" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Messvergleich" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Messvergleich'!$A$1:$G$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +28,36 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00315C69"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF0F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +72,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +452,255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ereignis</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Quelle</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wertung offen</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zeitpunkt</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Watch Puls</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Praxis Puls</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Watch Rhythmus</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Praxisbefund</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>04.03.2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Kauf</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Rechnung</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Beginn Frist</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>18.06.2026 09:12</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>unregelmäßig</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Sinusrhythmus</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>9.4.1</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>gleichzeitige Messung</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>18.05.2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Update</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>App-Log</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Auslöser möglich</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>18.06.2026 09:18</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Messung abgebrochen</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Sinusrhythmus</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>9.4.1</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Kontaktfehler</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>26.05.2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Mangelanzeige</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>E-Mail</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Zugang prüfen</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026 15:44</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Vorhofflimmern</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Sinustachykardie</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9.4.1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Praxisgerät dokumentiert</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10.06.2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Protokoll</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Nacherfüllung fraglich</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>24.06.2026 15:51</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>unregelmäßig</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Sinusrhythmus</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>9.4.1</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Uhr neu angelegt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>26.06.2026 11:08</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sinusrhythmus</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Werkstattreferenz</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9.4.1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>erster Werkstatttest</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>26.06.2026 11:16</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Abbruch</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Werkstattreferenz</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>9.4.1</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Kontakt prüfen</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -544,73 +711,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Betrag</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Beleg</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Dateistand</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Messwerte aus Praxiszettel, Nutzerexport und Werkstattprotokoll; keine medizinische Bewertung.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Kaufpreis</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1890</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Rechnung</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Servicepauschale</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>149</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Quittung</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ausweichlösung</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Kostennachweis</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Bearbeitung</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Rohdaten aus dem bezeichneten Vorgang; offene oder ungeprüfte Werte bleiben kenntlich.</t>
         </is>
       </c>
     </row>
